--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.008472363430969096</v>
       </c>
       <c r="C2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>31666569</v>
+        <v>4168090</v>
       </c>
       <c r="L2" t="n">
-        <v>18049301</v>
+        <v>2075075</v>
       </c>
       <c r="M2" t="n">
-        <v>4464772</v>
+        <v>428007</v>
       </c>
       <c r="N2" t="n">
-        <v>219780</v>
+        <v>10753</v>
       </c>
       <c r="O2" t="n">
-        <v>2651240</v>
+        <v>259231</v>
       </c>
       <c r="P2" t="n">
-        <v>1032116</v>
+        <v>99614</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999776482582092</v>
+        <v>0.9999932050704956</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8876538276672363</v>
+        <v>0.7980192899703979</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7811535000801086</v>
+        <v>0.6274111270904541</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7282065749168396</v>
+        <v>0.5293087363243103</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3892708718776703</v>
+        <v>0.1075213998556137</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7724358439445496</v>
+        <v>0.5876228809356689</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8552112579345703</v>
+        <v>0.7303133010864258</v>
       </c>
       <c r="X2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="AG2" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AH2" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AI2" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563413858413696</v>
+        <v>0.9555707573890686</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113937020301819</v>
+        <v>0.9118538498878479</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582093119621277</v>
+        <v>0.8584820032119751</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620789766311646</v>
+        <v>0.6613538861274719</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020217657089233</v>
+        <v>0.9020804166793823</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002030617636925397</v>
       </c>
       <c r="C3" t="n">
-        <v>699</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>31666569</v>
+        <v>4168090</v>
       </c>
       <c r="E3" t="n">
-        <v>3409249</v>
+        <v>806781</v>
       </c>
       <c r="F3" t="n">
-        <v>65084</v>
+        <v>21374</v>
       </c>
       <c r="G3" t="n">
-        <v>5967</v>
+        <v>1582</v>
       </c>
       <c r="H3" t="n">
-        <v>3585</v>
+        <v>1259</v>
       </c>
       <c r="I3" t="n">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="J3" t="n">
-        <v>70115366</v>
+        <v>10016579</v>
       </c>
       <c r="K3" t="n">
-        <v>75148022</v>
+        <v>10275505</v>
       </c>
       <c r="L3" t="n">
-        <v>86362589</v>
+        <v>11809795</v>
       </c>
       <c r="M3" t="n">
-        <v>106107905</v>
+        <v>15012443</v>
       </c>
       <c r="N3" t="n">
-        <v>113337931</v>
+        <v>16150881</v>
       </c>
       <c r="O3" t="n">
-        <v>109959882</v>
+        <v>15637237</v>
       </c>
       <c r="P3" t="n">
-        <v>112778929</v>
+        <v>16099308</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9008650779724121</v>
+        <v>0.8337612152099609</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7885939478874207</v>
+        <v>0.6311978697776794</v>
       </c>
       <c r="T3" t="n">
-        <v>0.683431088924408</v>
+        <v>0.4570043981075287</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3519549071788788</v>
+        <v>0.1201936006546021</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7434257864952087</v>
+        <v>0.5078559517860413</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7625353336334229</v>
+        <v>0.5147824287414551</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="Z3" t="n">
-        <v>1384204</v>
+        <v>196812</v>
       </c>
       <c r="AA3" t="n">
-        <v>59560</v>
+        <v>8425</v>
       </c>
       <c r="AB3" t="n">
-        <v>47621</v>
+        <v>6828</v>
       </c>
       <c r="AC3" t="n">
-        <v>247</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70116354</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>77619300</v>
+        <v>11107886</v>
       </c>
       <c r="AG3" t="n">
-        <v>89394449</v>
+        <v>12753027</v>
       </c>
       <c r="AH3" t="n">
-        <v>106848837</v>
+        <v>15260727</v>
       </c>
       <c r="AI3" t="n">
-        <v>113471912</v>
+        <v>16209880</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110391725</v>
+        <v>15769225</v>
       </c>
       <c r="AK3" t="n">
-        <v>112860888</v>
+        <v>16122838</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575594067573547</v>
+        <v>0.9575715065002441</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099474549293518</v>
+        <v>0.9095625281333923</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574531674385071</v>
+        <v>0.8570923805236816</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6615032553672791</v>
+        <v>0.6604667901992798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015399217605591</v>
+        <v>0.9011915326118469</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03203040203446905</v>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3772943</v>
+        <v>984168</v>
       </c>
       <c r="E4" t="n">
-        <v>18049301</v>
+        <v>2075075</v>
       </c>
       <c r="F4" t="n">
-        <v>944047</v>
+        <v>192864</v>
       </c>
       <c r="G4" t="n">
-        <v>39187</v>
+        <v>11035</v>
       </c>
       <c r="H4" t="n">
-        <v>76039</v>
+        <v>22262</v>
       </c>
       <c r="I4" t="n">
-        <v>6388</v>
+        <v>2114</v>
       </c>
       <c r="J4" t="n">
-        <v>988</v>
+        <v>43</v>
       </c>
       <c r="K4" t="n">
-        <v>4007889</v>
+        <v>1054954</v>
       </c>
       <c r="L4" t="n">
-        <v>5056658</v>
+        <v>1232286</v>
       </c>
       <c r="M4" t="n">
-        <v>1666417</v>
+        <v>380608</v>
       </c>
       <c r="N4" t="n">
-        <v>344814</v>
+        <v>89255</v>
       </c>
       <c r="O4" t="n">
-        <v>781071</v>
+        <v>181921</v>
       </c>
       <c r="P4" t="n">
-        <v>174739</v>
+        <v>36785</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999988853931427</v>
+        <v>0.9999966025352478</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8942106366157532</v>
+        <v>0.8154988288879395</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7848560810089111</v>
+        <v>0.6292987465858459</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7051087617874146</v>
+        <v>0.4905063509941101</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3696735799312592</v>
+        <v>0.1135049015283585</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7576532363891602</v>
+        <v>0.5448353886604309</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8062187433242798</v>
+        <v>0.6038932204246521</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1434717</v>
+        <v>207948</v>
       </c>
       <c r="Z4" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AA4" t="n">
-        <v>579437</v>
+        <v>82633</v>
       </c>
       <c r="AB4" t="n">
-        <v>38501</v>
+        <v>5536</v>
       </c>
       <c r="AC4" t="n">
-        <v>7988</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1536611</v>
+        <v>222573</v>
       </c>
       <c r="AG4" t="n">
-        <v>2024798</v>
+        <v>289054</v>
       </c>
       <c r="AH4" t="n">
-        <v>925485</v>
+        <v>132324</v>
       </c>
       <c r="AI4" t="n">
-        <v>210833</v>
+        <v>30256</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349228</v>
+        <v>49933</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569499492645264</v>
+        <v>0.9565700888633728</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106699824333191</v>
+        <v>0.9107067584991455</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578310608863831</v>
+        <v>0.8577865958213806</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617910265922546</v>
+        <v>0.6609100103378296</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017807841300964</v>
+        <v>0.9016357064247131</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>156173</v>
+        <v>50461</v>
       </c>
       <c r="E5" t="n">
-        <v>1394819</v>
+        <v>349051</v>
       </c>
       <c r="F5" t="n">
-        <v>4464772</v>
+        <v>428007</v>
       </c>
       <c r="G5" t="n">
-        <v>123727</v>
+        <v>26826</v>
       </c>
       <c r="H5" t="n">
-        <v>363069</v>
+        <v>73435</v>
       </c>
       <c r="I5" t="n">
-        <v>30283</v>
+        <v>8756</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3484720</v>
+        <v>831051</v>
       </c>
       <c r="L5" t="n">
-        <v>4838652</v>
+        <v>1212444</v>
       </c>
       <c r="M5" t="n">
-        <v>2068106</v>
+        <v>508542</v>
       </c>
       <c r="N5" t="n">
-        <v>404675</v>
+        <v>78711</v>
       </c>
       <c r="O5" t="n">
-        <v>915007</v>
+        <v>251211</v>
       </c>
       <c r="P5" t="n">
-        <v>321416</v>
+        <v>93893</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999913573265076</v>
+        <v>0.9999973773956299</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9344519972801208</v>
+        <v>0.8845039010047913</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9134323000907898</v>
+        <v>0.850288450717926</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9673290848731995</v>
+        <v>0.9455497860908508</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9934431910514832</v>
+        <v>0.9897140264511108</v>
       </c>
       <c r="V5" t="n">
-        <v>0.985162079334259</v>
+        <v>0.9734756350517273</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9956594705581665</v>
+        <v>0.9919974803924561</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56186</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>596891</v>
+        <v>86001</v>
       </c>
       <c r="AA5" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AB5" t="n">
-        <v>69704</v>
+        <v>9990</v>
       </c>
       <c r="AC5" t="n">
-        <v>204029</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1491842</v>
+        <v>212106</v>
       </c>
       <c r="AG5" t="n">
-        <v>2061119</v>
+        <v>297315</v>
       </c>
       <c r="AH5" t="n">
-        <v>931241</v>
+        <v>133840</v>
       </c>
       <c r="AI5" t="n">
-        <v>211376</v>
+        <v>30376</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351133</v>
+        <v>50436</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735060334205627</v>
+        <v>0.9733809232711792</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642549753189087</v>
+        <v>0.9640916585922241</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837567210197449</v>
+        <v>0.9837005138397217</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963063597679138</v>
+        <v>0.9962869882583618</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938730001449585</v>
+        <v>0.9938535690307617</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983745217323303</v>
+        <v>0.9983724355697632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>73766</v>
+        <v>17217</v>
       </c>
       <c r="E6" t="n">
-        <v>119391</v>
+        <v>22679</v>
       </c>
       <c r="F6" t="n">
-        <v>144393</v>
+        <v>28016</v>
       </c>
       <c r="G6" t="n">
-        <v>219780</v>
+        <v>10753</v>
       </c>
       <c r="H6" t="n">
-        <v>61720</v>
+        <v>9656</v>
       </c>
       <c r="I6" t="n">
-        <v>5348</v>
+        <v>1138</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45337</v>
+        <v>6558</v>
       </c>
       <c r="Z6" t="n">
-        <v>37466</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>76329</v>
+        <v>10994</v>
       </c>
       <c r="AB6" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AC6" t="n">
-        <v>48877</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>4798</v>
+        <v>3036</v>
       </c>
       <c r="E7" t="n">
-        <v>124889</v>
+        <v>49740</v>
       </c>
       <c r="F7" t="n">
-        <v>488556</v>
+        <v>128801</v>
       </c>
       <c r="G7" t="n">
-        <v>164111</v>
+        <v>44896</v>
       </c>
       <c r="H7" t="n">
-        <v>2651240</v>
+        <v>259231</v>
       </c>
       <c r="I7" t="n">
-        <v>132584</v>
+        <v>24725</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5670</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207844</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53148</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>8310</v>
+        <v>4035</v>
       </c>
       <c r="F8" t="n">
-        <v>24337</v>
+        <v>9553</v>
       </c>
       <c r="G8" t="n">
-        <v>11822</v>
+        <v>4916</v>
       </c>
       <c r="H8" t="n">
-        <v>276658</v>
+        <v>75309</v>
       </c>
       <c r="I8" t="n">
-        <v>1032116</v>
+        <v>99614</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
